--- a/reviews/a-envoyer/la-galerie-immobiliere-2026-09-28.xlsx
+++ b/reviews/a-envoyer/la-galerie-immobiliere-2026-09-28.xlsx
@@ -988,7 +988,7 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>2026-09-25T06:05:00</t>
+          <t>2026-09-25T10:04:49</t>
         </is>
       </c>
     </row>
